--- a/data/trans_orig/IP31KM05_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM05_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39297</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32791</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44899</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>53332</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45093</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>59691</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>74,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>63,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>46562</t>
+          <t>40752</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53953</t>
+          <t>45476</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>99894</t>
+          <t>80049</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87778</t>
+          <t>71481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110218</t>
+          <t>87892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20966</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15364</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27472</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>18068</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11709</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26307</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>25,31%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28045</t>
+          <t>14170</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36058</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>46113</t>
+          <t>35137</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35789</t>
+          <t>27294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>58229</t>
+          <t>43705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>81661</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72205</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>89900</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>71,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>96069</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>83976</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>76,46%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>89,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90343</t>
+          <t>69525</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79592</t>
+          <t>61109</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99740</t>
+          <t>77067</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>186411</t>
+          <t>151186</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171260</t>
+          <t>138372</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207617</t>
+          <t>163372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33290</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25051</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42746</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>28,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>29580</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13148</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>41673</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>33,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36080</t>
+          <t>29808</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26683</t>
+          <t>22266</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46831</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>65660</t>
+          <t>63098</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44454</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80811</t>
+          <t>75912</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>45985</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40643</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50039</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>80,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>70,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>39217</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33971</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43921</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>70,6%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51779</t>
+          <t>37798</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46050</t>
+          <t>32194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56265</t>
+          <t>42699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>90996</t>
+          <t>83783</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82346</t>
+          <t>76951</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98280</t>
+          <t>90923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11314</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7260</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16656</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>19,75%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>16335</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11631</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21581</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>29,4%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>11413</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>29189</t>
+          <t>27628</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37839</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>59580</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>50926</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65619</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>72,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93,99%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>48927</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41756</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55899</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>70,21%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59,92%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>80,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64757</t>
+          <t>49818</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55239</t>
+          <t>41521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70639</t>
+          <t>55883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>113684</t>
+          <t>109398</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102973</t>
+          <t>99216</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124544</t>
+          <t>118903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10236</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18890</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>20755</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13783</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27926</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20128</t>
+          <t>28941</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>31365</t>
+          <t>30880</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>21375</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42076</t>
+          <t>41062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,74 +2092,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38949</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36362</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>91,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>33333</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31141</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>91,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>34566</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32029</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35370</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>90,55%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40093</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>37553</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>92,22%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>135</t>
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>73426</t>
+          <t>73515</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70663</t>
+          <t>70914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74609</t>
+          <t>74696</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3217</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>804</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3059</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3166</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>39127</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>34596</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>42320</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>82,88%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>73,28%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>89,64%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>35237</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>30588</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>38637</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>79,56%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>69,06%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>87,24%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>44637</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39398</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>79873</t>
+          <t>74042</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73289</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85252</t>
+          <t>79593</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5653</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13702</t>
+          <t>12613</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>17453</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>11902</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24783</t>
+          <t>23950</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>110627</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>101393</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>119338</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>78,7%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>72,13%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>84,9%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>99822</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>88875</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>107264</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>80,7%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>71,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>86,72%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>122748</t>
+          <t>99662</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112607</t>
+          <t>91474</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133063</t>
+          <t>106334</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>222570</t>
+          <t>210289</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207760</t>
+          <t>196568</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>235541</t>
+          <t>220149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,9%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>29944</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>21233</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>39178</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>21,3%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>15,1%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>27,87%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>23874</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>16432</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>34821</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>22160</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42437</t>
+          <t>30348</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>56170</t>
+          <t>52105</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>43199</t>
+          <t>42245</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70980</t>
+          <t>65826</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>150785</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>143885</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>154467</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>95,96%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>91,57%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>120341</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>113552</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>124639</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>93,53%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>88,25%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>147843</t>
+          <t>128319</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>142527</t>
+          <t>119084</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>151210</t>
+          <t>133044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>268183</t>
+          <t>279103</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>260227</t>
+          <t>269855</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>273856</t>
+          <t>285341</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6351</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2669</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>13251</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8,43%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>8324</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>4026</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>15113</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>18816</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>15933</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9695</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22596</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>566010</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>547310</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>583530</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>82,41%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>79,69%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>84,96%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>734</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>526278</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>506008</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>547004</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>80,58%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>77,47%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>608760</t>
+          <t>495355</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>584740</t>
+          <t>478057</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>626642</t>
+          <t>510739</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,27 +3539,27 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1135038</t>
+          <t>1061364</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1105313</t>
+          <t>1036479</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1163495</t>
+          <t>1086227</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>120814</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>103294</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>139514</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>17,59%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>126856</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>106130</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>147126</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>19,42%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>22,53%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>135973</t>
+          <t>122853</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>118091</t>
+          <t>107469</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>159993</t>
+          <t>140151</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,22 +3652,22 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>262829</t>
+          <t>243667</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>234372</t>
+          <t>218804</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>292554</t>
+          <t>268552</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
